--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -73,6 +73,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -82,6 +88,12 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
@@ -89,6 +101,15 @@
   </si>
   <si>
     <t>RAMON</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>ODALYS</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>ABDIEL</t>
@@ -722,7 +743,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -754,16 +775,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920133</v>
+        <v>20330051920126</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -777,16 +798,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920137</v>
+        <v>20330051920127</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -800,16 +821,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920148</v>
+        <v>20330051920387</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -819,6 +840,75 @@
       </c>
       <c r="G4">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920133</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920137</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920148</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -79,9 +79,6 @@
     <t>ROSAS</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>MAYAHUA</t>
   </si>
   <si>
@@ -94,9 +91,6 @@
     <t>SALAZAR</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>XOCHIQUISQUI</t>
   </si>
   <si>
@@ -110,9 +104,6 @@
   </si>
   <si>
     <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
   </si>
   <si>
     <t>DAMARIS</t>
@@ -545,19 +536,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>70.97</v>
+        <v>77.42</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -636,7 +627,7 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -721,19 +712,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>70.97</v>
+        <v>77.42</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -743,7 +734,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -781,10 +772,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -807,7 +798,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -827,10 +818,10 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -844,16 +835,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920133</v>
+        <v>20330051920137</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -867,16 +858,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920137</v>
+        <v>20330051920148</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -885,29 +876,6 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920148</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
@@ -507,7 +507,7 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -516,13 +516,13 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -598,13 +598,13 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -683,7 +683,7 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -692,13 +692,13 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>93.09999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -73,40 +73,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
+    <t>TORRES</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>RAMON</t>
   </si>
   <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
+    <t>CONSTANZA XIMENA</t>
   </si>
   <si>
     <t>MEILYN ADABEL</t>
@@ -601,16 +580,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -624,16 +606,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>83.87</v>
+      </c>
+      <c r="H3">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -689,16 +674,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>93.33</v>
+        <v>80</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -715,16 +700,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>77.42</v>
+        <v>83.87</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +719,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -766,16 +751,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920126</v>
+        <v>20330051920151</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
         <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -789,16 +774,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920127</v>
+        <v>20330051920148</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -807,75 +792,6 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920387</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920137</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920148</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -73,19 +73,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>RAMON</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
   </si>
   <si>
     <t>MEILYN ADABEL</t>
@@ -719,7 +710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -751,16 +742,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920151</v>
+        <v>20330051920148</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -770,29 +761,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920148</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -73,13 +73,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>CONSTANZA XIMENA</t>
   </si>
 </sst>
 </file>
@@ -674,7 +683,7 @@
         <v>80</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,16 +700,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>83.87</v>
+        <v>96.77</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -710,7 +719,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -742,24 +751,47 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920148</v>
+        <v>21330051920031</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920151</v>
+      </c>
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -73,19 +73,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
   </si>
   <si>
     <t>CONSTANZA XIMENA</t>
@@ -719,7 +710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -751,47 +742,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920031</v>
+        <v>20330051920151</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920151</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="18">
   <si>
     <t>Mat</t>
   </si>
@@ -71,15 +71,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
   </si>
 </sst>
 </file>
@@ -691,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="H3">
         <v>7.2</v>
@@ -710,7 +701,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -740,29 +731,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920151</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
